--- a/src/attributions/attributions_ig_traj_440.xlsx
+++ b/src/attributions/attributions_ig_traj_440.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,55 +999,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.08608604857666213</v>
+        <v>0.09438465971049614</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2707430686247467</v>
+        <v>0.0693731074151443</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004001273688284372</v>
+        <v>-0.04684610196650853</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.05711919423029652</v>
+        <v>0.06838700610152301</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2424185176332642</v>
+        <v>-0.1283475727810018</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01439279748655964</v>
+        <v>-0.05757152081193433</v>
       </c>
       <c r="O2" t="n">
         <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1056,97 +1056,97 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1039938171523975</v>
+        <v>0.04361099847680138</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01705956103150915</v>
+        <v>-0.09630402083120278</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.01078891192103048</v>
+        <v>0.0649984135536824</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>-0</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-3.470842752942556e-11</v>
+        <v>1.089001772518747e-11</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.006287610896074329</v>
+        <v>-0.01960132095109602</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.992104022987901e-12</v>
+        <v>-4.16893482432144e-12</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.04586640419228727</v>
+        <v>0.1641225145531063</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.04249581251515201</v>
+        <v>-0.03131995077464074</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07080012785383533</v>
+        <v>0.2710039674868375</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1675629633249888</v>
+        <v>0.2975201651246753</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09601824582853803</v>
+        <v>-0.01060278056500983</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.01667735686670889</v>
+        <v>0.02809333447271138</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
@@ -1158,22 +1158,22 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.007563276064319164</v>
+        <v>-0.02173023135432557</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1049887927948767</v>
+        <v>0.06247681882603298</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.004555816567386153</v>
+        <v>-0.01052640594763228</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
@@ -1182,55 +1182,55 @@
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01855919159624354</v>
+        <v>-0.08418048983873082</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.03870817360056667</v>
+        <v>-0.07220136019417482</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.08014909847657475</v>
+        <v>-0.009683130096866334</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.06240362818182101</v>
+        <v>0.1423800041598501</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.02238961253711967</v>
+        <v>-0.1419600935362539</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.02819281016782701</v>
+        <v>0.02910652211709572</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
         <v>-0</v>
@@ -1245,16 +1245,16 @@
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.03017968464745394</v>
+        <v>-0.1516806508669531</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.04373135439866592</v>
+        <v>-0.02379494063707738</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01555492970330826</v>
+        <v>-0.02861223537144704</v>
       </c>
       <c r="CI2" t="n">
         <v>0</v>
@@ -1263,52 +1263,52 @@
         <v>-0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.01683645637809813</v>
+        <v>-0.1092740536045164</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.02927517608387242</v>
+        <v>0.1277773100754441</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.05732951286099017</v>
+        <v>-0.06077658895932891</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.04485442205455682</v>
+        <v>-0.1512332769463312</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.04610213201090916</v>
+        <v>-0.01624816320360194</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.007004487323011817</v>
+        <v>0.0004415440536947207</v>
       </c>
       <c r="DA2" t="n">
         <v>-0</v>
@@ -1317,34 +1317,34 @@
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
         <v>0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.03663010099907456</v>
+        <v>-0.05987723714449283</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.01496390616943506</v>
+        <v>0.09079409155468805</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.03101452545121341</v>
+        <v>-0.01293999666007039</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK2" t="n">
         <v>-0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
         <v>-0</v>
@@ -1353,19 +1353,19 @@
         <v>0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.02091649284860365</v>
+        <v>-0.05436453728523589</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.04285491153331428</v>
+        <v>0.0281992413081069</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.03731491465691677</v>
+        <v>-0.01542486031223231</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1377,22 +1377,22 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.05320440195189079</v>
+        <v>0.01252600781858442</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.002892739116739693</v>
+        <v>0.1539204528243243</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.03046001104498006</v>
+        <v>0.1659729650577228</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
@@ -1407,22 +1407,22 @@
         <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.04214883444383082</v>
+        <v>-0.1359199299212554</v>
       </c>
       <c r="EH2" t="n">
         <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.09694243965812084</v>
+        <v>0.1651021329437624</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.02535434639816732</v>
+        <v>0.03912596760247919</v>
       </c>
       <c r="EK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
@@ -1434,46 +1434,46 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.0523474947198154</v>
+        <v>-0.06906209200691744</v>
       </c>
       <c r="EQ2" t="n">
         <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.0505857322256974</v>
+        <v>0.01740309267925701</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.02099614862398629</v>
+        <v>0.004083868872674844</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.03977438091833668</v>
+        <v>-0.1903166614372621</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.03758484801388312</v>
+        <v>0.0102788196653512</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.01722156883334725</v>
+        <v>-0.005801414418240494</v>
       </c>
       <c r="FC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD2" t="n">
         <v>-0</v>
@@ -1488,76 +1488,76 @@
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.006986232390577869</v>
+        <v>-0.1540650545050549</v>
       </c>
       <c r="FI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.0160849485541347</v>
+        <v>-0.04100523188880333</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.02278434274117715</v>
+        <v>0.03785039104431163</v>
       </c>
       <c r="FL2" t="n">
         <v>-0</v>
       </c>
       <c r="FM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.009903314644151768</v>
+        <v>-0.1201300836813321</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.01161490472161882</v>
+        <v>0.2197798068796776</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.00335253712351679</v>
+        <v>-0.007413224886760936</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW2" t="n">
         <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
         <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03276389726031452</v>
+        <v>-0.03916712419804527</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.02249852629173317</v>
+        <v>-0.01180588806445407</v>
       </c>
       <c r="GC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD2" t="n">
         <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
         <v>-0</v>
@@ -1568,241 +1568,241 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>-0.000492898816724477</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0.0008506149910854886</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>-0.0008865178592570605</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-0.001630609408557188</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>-0.003028293747250138</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.001298147718802626</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.01019543147278897</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0</v>
+        <v>0.003762306451083474</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>-0.004386827739145949</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-5.897989178836727e-12</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0</v>
+        <v>4.125971766911385e-12</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>-7.044888168136423e-12</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.005099322553286502</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0</v>
+        <v>0.006039160051190093</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.003228475785735994</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.006816450979741958</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0</v>
+        <v>0.0175054323696083</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0.00306407171064633</v>
       </c>
       <c r="BA3" t="n">
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0.001316002558839378</v>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF3" t="n">
         <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0</v>
+        <v>-0.001927991320239698</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.0002086423365392996</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.002041969141449034</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0</v>
+        <v>0.008083587201371027</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0.002193871975902119</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.009013215920843604</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0</v>
+        <v>0.006663043662937612</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>-0.00412468231670458</v>
       </c>
       <c r="CB3" t="n">
         <v>0</v>
@@ -1811,34 +1811,34 @@
         <v>0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.0005038963513780533</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0</v>
+        <v>-0.005167542129589739</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.001289029891499301</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.0005207676086109091</v>
       </c>
       <c r="CN3" t="n">
         <v>0</v>
@@ -1847,97 +1847,97 @@
         <v>0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0</v>
+        <v>-0.02178583154158514</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.00788377676128495</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.002437022863833347</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY3" t="n">
         <v>0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>-0.007368772533915784</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.002533796546038462</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>-4.054886706900379e-05</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>-0.01205746464359991</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.00164864834291333</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.00783639030704744</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0</v>
+        <v>-0.01634251150256602</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.0004839414874218308</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1946,115 +1946,115 @@
         <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.006733163145322421</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0</v>
+        <v>0.004938359531460971</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.01215720040246038</v>
       </c>
       <c r="ED3" t="n">
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.004332833682076213</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>-0.002817999550062541</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.0001033116370360131</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0.002016928939972156</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0</v>
+        <v>-0.008531337799519824</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.003396143179071419</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.00203208388507665</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ3" t="n">
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0</v>
+        <v>-0.008630986685323631</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.004951108782687784</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.00402543880905007</v>
       </c>
       <c r="FH3" t="n">
         <v>0</v>
@@ -2063,25 +2063,25 @@
         <v>0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0</v>
+        <v>0.01011928700515337</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0.003972065311792949</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0.01536549142926059</v>
       </c>
       <c r="FQ3" t="n">
         <v>0</v>
@@ -2093,46 +2093,8581 @@
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0</v>
+        <v>0.004447069542214008</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0.002576953152250918</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>-0.001871881302383306</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01067770256279193</v>
       </c>
       <c r="GF3" t="n">
         <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.2439461587672551</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.06944671040123411</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1416571700002332</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.2446482104823363</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.1046160421306596</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.07957215588611424</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-0.07129538996513848</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1011103211571849</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1503781302419677</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-5.282371375284531e-11</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>5.63666995744401e-11</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-4.105899425517552e-11</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-0.2598726829037356</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>-0.2746455590009633</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.07021772927558904</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>-0.5815478359113649</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.1245622558484485</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.1549794272988964</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.003058404305189835</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.001606090707028727</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.007576470997498415</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.1039864022525436</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>-0.07808702761969802</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>-0.03495911271592456</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>-0.4587947294964351</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.05676059256052986</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.2451641359941036</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.3173360473935407</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>-0.02021460568243656</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>-0.1372001419069401</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.3075241712726262</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.02157571842218051</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>-0.141069610867712</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.312537188787327</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>-0.03658259444175247</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>-0.1430838455517289</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.05306100454814014</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.0178772174118181</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>-0.03916198970084165</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.1776074631027078</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>-0.02404462181895744</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>-0.02938485369219356</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>-0.175545956203529</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>-0.01990208081661439</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.2825953422790284</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.2158843214602992</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>-0.04216087590762251</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>-0.08323330756854383</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.1833155999494198</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>-0.06600494237601699</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>-0.00964185084665603</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.3369120998673907</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>-0.0165182634749593</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>-0.1335250968115999</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.1002171728695255</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.08673419120711141</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>-0.01441601745665192</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.3394252537287261</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.07532618268338452</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>-0.2296679330551563</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.1885729905727712</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>-0.0670984500313816</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.002811605864348432</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.02762870802926924</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.008017593048523867</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.007534397033419188</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.03953757569681044</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.005708175060547072</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>-0.001239878920027033</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.01338769776802348</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.007692561142075787</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>5.908979965716168e-13</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-3.387449931206339e-12</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-5.008869327410907e-12</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.002175307225658456</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>-0.01600877396713143</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>-0.009096510056941304</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.0186519412337554</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.05461865376565121</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>-0.009567124434310461</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>-0.01266175053835638</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.001516724099531118</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>-0.001002628874460499</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.007562857527816953</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.01256699189091099</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.01303133555289179</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>-0.01428737610006251</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.02762436812011974</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>-0.01153682300113765</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.006149965041385509</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>-0.01586800876373396</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.01250620595726649</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.01989015839225226</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.003376614700617632</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.01427912864727498</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.005113232859842989</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>-0.01905621018827061</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.01352207905474705</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0.001269922403640437</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>-0.003984616371409084</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>-0.0009424032707592575</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.01523599999138949</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>-0.01493516621617913</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>-0.003447913364232838</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>-0.007358233990862305</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>-0.01760682438899118</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0.002712140801452384</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0.006923349611502703</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>-0.01693416815802855</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0.009027747180216544</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0.003367842749585827</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>-0.02723196238931651</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0.009257426945897916</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0.002979945170829072</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>-0.01554031493566747</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0.01351575692009846</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>-0.01774887565957049</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>-0.0003780541009860833</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0.02226157517185869</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>-0.01952622123515659</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>-0.04508818879700995</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0.003140604502572304</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>-0.02205086465079261</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0.01567993382591273</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0009283142420477869</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.01182602969442543</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.01824936787979095</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.003112686830188585</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01003714117996499</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-0.01670603531364613</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.0001074069944380935</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.01209672553458769</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.00404557483671512</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-0.009521925790160446</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.0005406297023450289</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.852302500506845e-11</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-0.01513009854381047</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.01593539510633358</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.003120253270502335</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>-0.0225498787316839</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.03734866032584279</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-0.03735525857068782</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.0003966114558114356</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-0.01227465087178735</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>-0.01196253985430001</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.005382745876548574</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.0297811448436138</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.03700380182214601</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>-0.001540580597873858</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.02602006617422839</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.0003934313149074308</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.01019698003662915</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.003974709626232037</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.005561903579116302</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>-0.001130640193069934</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.01616511454815064</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.02866040853158743</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.006954815480467956</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.002777719298672397</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.008477984820420441</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.004671730539411847</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>-0.01424417749889241</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.001803823280493877</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>-0.004485854088485663</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>-0.01258601541810652</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.02501837725644156</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>-0.02178397042564851</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>-0.008102343230826184</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>-0.01483727115363042</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>-0.002859007003898484</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.0009378457526238661</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>-0.004977061789506756</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>-0.003809835396911014</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>-0.002609619246766426</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.01377572290495475</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.005342214411510279</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>-0.001358703614770268</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.007904626955298638</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.01021069220961661</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.008764197883975092</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>-0.02749428532521471</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.0003372502505331237</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.0008344545098187793</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.01840654130913709</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>-0.001521393919083219</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>-0.02035831114130728</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0.1161394201519243</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.03410180197463717</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.03809875056089151</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1757384722581325</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-0.07604841824624617</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.04531733195301886</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.0764687873683467</v>
+      </c>
+      <c r="U8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>-0.03907818920661758</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.02600650657197913</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.02153791065801643</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.02339453667908659</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.006376043227555335</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.0286163871147699</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>-0.02728586960578488</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.03861184419041595</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.276690839256556</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>-0.1353675644957287</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>-0.128377503583628</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>-0.03017115423565566</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>-0.01825807491974981</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0.007182296619160127</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.05717418220625626</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.08635957192713105</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0.06308607595235889</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0.2006124505380221</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>-0.03573028048247359</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>-0.01847558621123575</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>-0.05259543113609558</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.0312052413909738</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.0256831572972147</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>-0.07637329278424125</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0.07808431837662462</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>-0.004661537176928546</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>-0.04888867279163252</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0.02263070003860308</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0.03114302942203134</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>-0.04843097598435273</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>-0.004747450232604839</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.003113248757310741</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>-0.005869232969880059</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>-0.0001324046734440395</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>-0.01178506719798565</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0.05718243536110411</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>-0.09587320744538141</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0.02104119667410272</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0.01168370714244719</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>-0.02219253851564371</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0.007411938307853813</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>-0.005019668748669575</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>-0.09631100293662644</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0.01969273354280289</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>-0.05618793396304412</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0.01203230972773534</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0.016805952728509</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>-0.03882928398055838</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0.05694512933865339</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0.004786629029941081</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0.006580457977096192</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>-0.02132471258139589</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>-0.06839529473171303</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>-0.05737776400755509</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0.05143185218007416</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.211985735818394</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.08258137857372908</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01328590414228812</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2514350634452777</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.1122272642215672</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.00724837868423726</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.07551812761478663</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-0.03788832195916397</v>
+      </c>
+      <c r="W9" t="n">
+        <v>-0.05882124743802111</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.0201734307913567</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>-0.0325247255790161</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>-0.001085348860896964</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.1027927186335985</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.04840328248800564</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0.05493451078386974</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.2551206771576999</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.06021222292154151</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.07067276129080989</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.01317425766658943</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>-0.02901566439787782</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>-0.01754199162137065</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>-0.008033213370564311</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>-0.01453233886085489</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.03354838719729268</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.2015412846961568</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>-0.0592643313024858</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>-0.02939447697102445</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>-0.09404842278865294</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.07332894444750745</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>-0.02610391990001537</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>-0.0667758576155143</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.1421134395864473</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>0.03201969186506635</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>-0.08616104544145249</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.07534597626975924</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>-0.01593410440630358</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>-0.0639395846912145</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.009823481168435922</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>-0.04733567611072687</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>-0.06422985613180487</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.05880161106089628</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>-0.01972746083878944</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.03946871775561388</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>-0.04744878921027058</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.0471172653566773</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>-0.06825953085860073</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>0.05447607452360693</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>-0.01187105793437727</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>-0.02519774973452734</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>0.002487137728226333</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>-0.009019122408944364</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>-0.1027349486469313</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.07860010344874466</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>-0.0246752872077785</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>-0.05791388726902776</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.05029952359205329</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>-0.001711176992606162</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.003297953085269098</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.03077705792112054</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>-0.01433822300621203</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>-0.08394052884481293</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>0.02880752215249442</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.2567115508451135</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-0.005686148607425996</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.05988912968335414</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.3805281818899648</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.0614611176642155</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.05060208801571617</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.06649360259586873</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>-0.05455792698952775</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.01673062232089503</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>-0.009976524991144925</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>-0.07847109985866139</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>-0.03475594847096719</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.06637502103969346</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.03302694734909691</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>-0.02539343374816045</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0.3767160537000388</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>-0.1373893709137139</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>-0.05515660213003076</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0.008520441692125954</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>-0.0387901857814731</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>-0.03079929797510328</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.02670040589214907</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.05509697627679296</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>-0.004049004626796598</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0.2554881266734981</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>-0.02682187890461703</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>-0.03815966336703472</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>-0.1098444853534705</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.006579599131111395</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0.05594453468272321</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>-0.1882799064473744</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0.09948545591318775</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0.07109263211376533</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>-0.1119675691241921</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>-0.01060993627960564</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0.0520469476090327</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>-0.04577453574442274</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>-0.1367003822294791</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.0224994330573997</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>-0.09915257267223372</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.05387868815458405</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>-0.007188186804855353</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>-0.0124201275136171</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0.08105107734885146</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>-0.1078337949108438</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>-0.02123601165217517</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>-0.05031749454935468</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0.02430052384181043</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>-0.004594645909258692</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>-0.08870376232135782</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0.04659596743546911</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>-0.1254801547236861</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>-0.01631756392919324</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0.04399205153320806</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>-0.166659615150877</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0.1022716747951878</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0.01286641264503024</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0.001932743356747491</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>-0.00542035362053293</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>-0.03199888739989271</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>-0.02725596251317285</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0.004320742469379178</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.260578885071462</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.1180725213413954</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.03787008692732969</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.2861987011680039</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.1767872312615215</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-0.08118163386962955</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.07255949055179867</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-0.05446305183961782</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.06528803802038902</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-0.04882154278152735</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>-0.05812376107767864</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>-0.06607531660720592</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1218004605768027</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>-0.04462760891350588</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.0686462450287207</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.3441779717788283</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>-0.08014925493097631</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>-0.1359250447019642</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.035977694695205</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>-0.0210366744898917</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>-0.03461952221008272</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>-0.0004940422450920595</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>-0.002551157579756763</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.05170339026848187</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.2615636679089712</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>-0.1065931521663205</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>-0.05326377507176269</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>-0.113614412417744</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.07700025946578846</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.01204473950598159</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>-0.1059177660304846</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.1546546945724335</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.05738150587023443</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>-0.1076504616750549</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.08806218891849876</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.009732569016452232</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>-0.06841791250181262</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.02795692115991846</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>-0.05259811646129335</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>-0.04046163237030035</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.0004266067190140261</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>-0.0191060951204505</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.1124029504273153</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.05260481260699411</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>-0.04681004058076506</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>-0.05468765966272697</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.05162664328036631</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.03419364689893844</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>-0.04344794868912145</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.07790766007698544</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>-0.06513296426944946</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>-0.1242366672587818</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.09521261143066424</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>-0.005330176149197032</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>-0.03795236854287641</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.06975467978925143</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>-0.01257603636469524</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.0004087778447526459</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.07263221644417615</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>-0.003945284103857665</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>-0.09130109076787718</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.0497581568116039</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.4403429855924919</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.1244588906419472</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.3573275403602778</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7181222349732124</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.02525456695787872</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.3927443756946662</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.2220988734977141</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.1940909272794008</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.03042306134382886</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.06293543913970813</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>-0.3133987195488411</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>-0.1959727216429111</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.1626272370159441</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.008053306844531342</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>-0.249861000962278</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.023123831738067</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>-0.05912599473448602</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>-0.2607892148252819</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>-0.1165427248832331</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>-0.1751402486170377</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>-0.2082273174326935</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.197040228668892</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>0.2118948681990397</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>-0.005450101236091302</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>0.5737857596671685</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>-0.0655362404611531</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>-0.2408412590111305</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>-0.2171628471686366</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.01010027465048202</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.1767904844139851</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>-0.5315221390241985</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>0.2636126232589538</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>0.3433682480554994</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>-0.2117323220571365</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>-0.05512531286808706</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>0.162744136590544</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>-0.01788755370189976</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>-0.2264600710390211</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.02027571235977396</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>-0.04948465176344614</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>-0.01087074367971267</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0.03347328884734276</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>0.1396808858099517</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>0.009777856486582323</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>0.07834043156010098</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>-0.01118814548614527</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>-0.1518695308910662</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>0.04270704406678973</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>-0.03234290236055151</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>-0.1447206449678439</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>0.1022275499346468</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>-0.2364826994918215</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>-0.08061522864279777</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>0.1600396036627237</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>-0.2489651956683366</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>0.1574179283838816</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>-0.2157145414444646</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>-0.05368933353243571</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>0.0006488956690884453</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>0.06979590523105909</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>-0.02077349225618502</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>-0.04588211495268259</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.0366693513914572</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.3005794428041597</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.07115458593468207</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-0.01437181680223647</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.4060575162893224</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.07334949511564423</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-0.01701498298800208</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-0.03108287433694841</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.2784496260968693</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.06057259024711637</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.07133657480888045</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2485611248845102</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>-0.01859233003383423</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>-0.1998057208374013</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1921438729106745</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>-0.001128035503456145</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>-0.4778452477645736</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.2605177747588979</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-0.08672499246136987</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>-0.07612312968538715</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>-0.07812507873405412</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.1014571317402991</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>-0.127827653956172</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>-0.2728031539255883</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>-0.02460806894077286</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>-0.2120907208069209</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.2057282513117803</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>-0.01440326815744891</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.08488801375693675</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>-0.05792730885907588</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.1582802427007775</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.1764098129773055</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>-0.06235595580969199</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>-0.002091825322826272</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.08313715333916009</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>-0.03581984882764026</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.02988322751472722</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.03524781607179536</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.001189904406566586</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.02148757772044754</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.1219976795149675</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.07366899060880708</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.02783711235857732</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.2418560028765334</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.2917503098938448</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.01634331829605451</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.01245265713428991</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.006707369602653321</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>-0.01948318184423935</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.01318184335667505</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>-0.01244106220295528</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>-0.01128505243266603</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.09717323786107294</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>-0.03047027330870004</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.01857439141760082</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.1803427191228496</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.1213000837143632</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>-0.001735311551240222</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>-0.00285211470412785</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>-0.05123063361373829</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.04691699275809349</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.04084432979825237</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.3545828212686763</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-0.1991372222818531</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.07419528011378325</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.5317029307753016</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.2997101625788739</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-0.1087512605346057</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.02708640547414473</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.1083912036825737</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.01983309517795192</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.01383370403387296</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>-0.1039956246144523</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.008421021044543406</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.1370047909112817</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>-0.02358799507556461</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0.02203366721596657</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.4707223109756103</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>-0.1740839964733349</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.01019495527010819</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>-0.04270679360592765</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>-0.07260411051813248</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>-0.05963286244787001</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.09122587435082521</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.1283736531319084</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.0404346239193179</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.3065848694895895</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>-0.1499550881630424</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>-0.04060977199928734</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>-0.1412784218516184</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.05352478956169792</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.02610441452158619</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>-0.2385129047129514</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.02715975222447897</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>-0.004458144553206122</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>-0.1312277601510701</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.02975361429624733</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>0.02891599637899607</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>-0.02961034249346532</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>-0.1041828483442449</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>-0.07614706244463255</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>-0.08493573190070969</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>0.001160407161428532</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>-0.01407654548936669</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.08934021868537179</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.009800844020228808</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.05777962240642723</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>-0.0401055623449924</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>-0.01607858878486162</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>0.01758761521123939</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>-0.05795361737981648</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.009872192204333264</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.06013705484805655</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>-0.1606725163840855</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.02255678963357994</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>0.03855766347935955</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>-0.08349358399901825</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.09201888681952491</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.0642152391244718</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>-0.002262050785536415</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.002046802179052992</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>-0.00094535526774349</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>-0.04100032024613815</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.06198528855676559</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>-0.02372056941707217</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.04131643732160385</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.02162038146857253</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-0.01825916109202654</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.06852518384885566</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.02477424798838624</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.005536596808011051</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.01158359640925321</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.001027120168831855</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.002113451911267596</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-0.00432959099537644</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>-0.004875089248281705</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.0002488613279908987</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0.01269946676217871</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-0.007202944514552173</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>-0.006753489854071193</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.03777836907702553</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>-0.02405494863417618</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>-0.01696380532700793</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0.008083584745928411</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>-0.01641288060446598</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>-0.001556419968043042</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0.01139177698831306</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0.03067270109513913</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0.005778395511794299</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0.03486235087994485</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>-0.008083963932858986</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0.00846789383597101</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>-0.01321815831414361</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0.007228785096199225</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>-0.002237155044846617</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>-0.03146331233344878</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0.0173253199075242</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0.007046897657787903</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>-0.01393856912233623</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0.003075994520562241</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0.005639751979740029</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>-0.03194025957013532</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0.0002073957861581678</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0.003302379888104384</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>-0.009453250971730776</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>-0.009034407493439462</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0.007143814600959794</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0.01605696866330404</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>-0.003915224126056376</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>-0.001743608811522281</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>-0.002427774456461721</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0.0008238929763544519</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0.00199075505787367</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0.003082732789867499</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>-0.00755196132686958</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0.009125890362272611</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>-0.01738714511535258</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0.002798290972606765</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0.004204356067796225</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>-0.009197972184496719</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0.0199435895328564</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0.003260733313313482</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0.001008745442009065</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0.002357171552738183</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0.01090995520939297</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>-0.01104206562405361</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1498876840207892</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.1364141933736148</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-0.0181631556956894</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.2064975568254803</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-0.2092378522263859</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-0.04940106228036183</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.07079550449098998</v>
+      </c>
+      <c r="U16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.009205968607524101</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.01523740754668955</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-0.02784208910394309</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>-0.08371206247206253</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0.02193226356156847</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.07053153116675775</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0.01135144812868481</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>-0.01091747899311669</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.21319796836691</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>-0.05404260259631689</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>-0.01071582486017519</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>-0.06424938677928504</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.05385332686866674</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>-0.02175083034753827</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.01816080407422527</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>0.09600022582213363</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>0.03629434371017379</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>0.1972814618110984</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>-0.02892477512729887</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>0.01196444297906586</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>-0.07219594852030808</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>0.0568909124444956</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>0.002275289988846612</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>-0.1244590333355436</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>0.01769701983596822</v>
+      </c>
+      <c r="CR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>0.0008410263261037112</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>-0.06549972757007869</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>0.05196406970298974</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>0.01558049705673411</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>-0.09255226131075805</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>-0.01761381686275465</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>-0.02782012491677582</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO16" t="n">
+        <v>-0.02675991577104927</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>0.0563234503730474</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.01657187547259482</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>0.05413266715387655</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>-0.05352780952281946</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EC16" t="n">
+        <v>-0.009665169472749882</v>
+      </c>
+      <c r="ED16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG16" t="n">
+        <v>-0.03050618124029291</v>
+      </c>
+      <c r="EH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ16" t="n">
+        <v>0.023933419586733</v>
+      </c>
+      <c r="EK16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EL16" t="n">
+        <v>-0.01143996112028552</v>
+      </c>
+      <c r="EM16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP16" t="n">
+        <v>-0.04836572236002094</v>
+      </c>
+      <c r="EQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ES16" t="n">
+        <v>-0.006764729506276938</v>
+      </c>
+      <c r="ET16" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU16" t="n">
+        <v>0.0190347454789135</v>
+      </c>
+      <c r="EV16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY16" t="n">
+        <v>-0.07537863319837283</v>
+      </c>
+      <c r="EZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FB16" t="n">
+        <v>0.03977439090055263</v>
+      </c>
+      <c r="FC16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FD16" t="n">
+        <v>0.0002805137058748994</v>
+      </c>
+      <c r="FE16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH16" t="n">
+        <v>-0.02977305192953052</v>
+      </c>
+      <c r="FI16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FK16" t="n">
+        <v>-0.00238519507279046</v>
+      </c>
+      <c r="FL16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FM16" t="n">
+        <v>-0.02780115891472282</v>
+      </c>
+      <c r="FN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FP16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ16" t="n">
+        <v>-0.004262832548478069</v>
+      </c>
+      <c r="FR16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FT16" t="n">
+        <v>-0.0006412981209867683</v>
+      </c>
+      <c r="FU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV16" t="n">
+        <v>-0.02823501201817321</v>
+      </c>
+      <c r="FW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ16" t="n">
+        <v>-0.04499924648852983</v>
+      </c>
+      <c r="GA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE16" t="n">
+        <v>-0.009704480770243513</v>
+      </c>
+      <c r="GF16" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GG16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER17" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ET17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT17" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-0.3350511691159093</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2918784289450576</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2254039522531619</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.3827618363625123</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.4739374422213596</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2812466117708723</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.06079196189306236</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.05665734576829226</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.01158448582033745</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.0431379467496141</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.07435637498327544</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.06540144884474253</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>-0.2044893153308514</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.03306437972438154</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>-0.2128464081588029</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>-0.5129365673541126</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0.09139728839416575</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.130562653868143</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0.09720357722809783</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0.1108832940219397</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.1868910663891738</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.09804128808749345</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>-0.01639128221932321</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>-0.02221794239396222</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV18" t="n">
+        <v>-0.3275335354724262</v>
+      </c>
+      <c r="BW18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="BX18" t="n">
+        <v>0.1823546921406823</v>
+      </c>
+      <c r="BY18" t="n">
+        <v>0.05967607341631333</v>
+      </c>
+      <c r="BZ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CE18" t="n">
+        <v>0.197888492854103</v>
+      </c>
+      <c r="CF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG18" t="n">
+        <v>-0.09492263242996703</v>
+      </c>
+      <c r="CH18" t="n">
+        <v>-0.009942173313494781</v>
+      </c>
+      <c r="CI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CN18" t="n">
+        <v>0.1979153523244146</v>
+      </c>
+      <c r="CO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP18" t="n">
+        <v>-0.2525537709634357</v>
+      </c>
+      <c r="CQ18" t="n">
+        <v>-0.1126649565005415</v>
+      </c>
+      <c r="CR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW18" t="n">
+        <v>0.1977042645155877</v>
+      </c>
+      <c r="CX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="CY18" t="n">
+        <v>-0.1054206641636186</v>
+      </c>
+      <c r="CZ18" t="n">
+        <v>-0.03037319858350699</v>
+      </c>
+      <c r="DA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DB18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DF18" t="n">
+        <v>0.04918202867661803</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>-0.1105866557255497</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.01849438182172237</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DO18" t="n">
+        <v>0.0748858532914841</v>
+      </c>
+      <c r="DP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>-0.05749779092765403</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>0.07931142132178826</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>-0.06854441440130991</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>-0.06773619744201057</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>-0.007867880610552883</v>
+      </c>
+      <c r="EB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EG18" t="n">
+        <v>0.2006469187917476</v>
+      </c>
+      <c r="EH18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EI18" t="n">
+        <v>-0.03356676119331643</v>
+      </c>
+      <c r="EJ18" t="n">
+        <v>-0.06021994674353744</v>
+      </c>
+      <c r="EK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EP18" t="n">
+        <v>0.1135436331762059</v>
+      </c>
+      <c r="EQ18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="ER18" t="n">
+        <v>-0.05986646333385267</v>
+      </c>
+      <c r="ES18" t="n">
+        <v>-0.03244833617190705</v>
+      </c>
+      <c r="ET18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="EY18" t="n">
+        <v>0.2344171159129403</v>
+      </c>
+      <c r="EZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA18" t="n">
+        <v>-0.1297286575581099</v>
+      </c>
+      <c r="FB18" t="n">
+        <v>-0.03411389058439795</v>
+      </c>
+      <c r="FC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FH18" t="n">
+        <v>0.1123909793276081</v>
+      </c>
+      <c r="FI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ18" t="n">
+        <v>0.07844988951381356</v>
+      </c>
+      <c r="FK18" t="n">
+        <v>-0.01751930145807183</v>
+      </c>
+      <c r="FL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FQ18" t="n">
+        <v>0.1427183356207509</v>
+      </c>
+      <c r="FR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS18" t="n">
+        <v>-0.07314472079688968</v>
+      </c>
+      <c r="FT18" t="n">
+        <v>-0.01213214324558594</v>
+      </c>
+      <c r="FU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FY18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="FZ18" t="n">
+        <v>0.1669041671890789</v>
+      </c>
+      <c r="GA18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GB18" t="n">
+        <v>-0.03916270300614899</v>
+      </c>
+      <c r="GC18" t="n">
+        <v>-0</v>
+      </c>
+      <c r="GD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG18" t="n">
+        <v>-0</v>
       </c>
     </row>
   </sheetData>
